--- a/artfynd/A 33708-2025 artfynd.xlsx
+++ b/artfynd/A 33708-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128248892</v>
       </c>
       <c r="B2" t="n">
-        <v>92286</v>
+        <v>92287</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         <v>128248980</v>
       </c>
       <c r="B3" t="n">
-        <v>92286</v>
+        <v>92287</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 33708-2025 artfynd.xlsx
+++ b/artfynd/A 33708-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128248892</v>
       </c>
       <c r="B2" t="n">
-        <v>92287</v>
+        <v>92295</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         <v>128248980</v>
       </c>
       <c r="B3" t="n">
-        <v>92287</v>
+        <v>92295</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 33708-2025 artfynd.xlsx
+++ b/artfynd/A 33708-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128248892</v>
       </c>
       <c r="B2" t="n">
-        <v>92295</v>
+        <v>92387</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         <v>128248980</v>
       </c>
       <c r="B3" t="n">
-        <v>92295</v>
+        <v>92387</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 33708-2025 artfynd.xlsx
+++ b/artfynd/A 33708-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128248892</v>
       </c>
       <c r="B2" t="n">
-        <v>92387</v>
+        <v>92399</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         <v>128248980</v>
       </c>
       <c r="B3" t="n">
-        <v>92387</v>
+        <v>92399</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 33708-2025 artfynd.xlsx
+++ b/artfynd/A 33708-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128248892</v>
       </c>
       <c r="B2" t="n">
-        <v>92399</v>
+        <v>92401</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         <v>128248980</v>
       </c>
       <c r="B3" t="n">
-        <v>92399</v>
+        <v>92401</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 33708-2025 artfynd.xlsx
+++ b/artfynd/A 33708-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128248892</v>
       </c>
       <c r="B2" t="n">
-        <v>92401</v>
+        <v>92402</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         <v>128248980</v>
       </c>
       <c r="B3" t="n">
-        <v>92401</v>
+        <v>92402</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 33708-2025 artfynd.xlsx
+++ b/artfynd/A 33708-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -906,6 +906,122 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>128832151</v>
+      </c>
+      <c r="B4" t="n">
+        <v>102863</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>CR</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>223246</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Skogsalm</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Ulmus glabra</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Huds.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Marma gård, 540 m SSO om, Upl</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>667000</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6640743</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Almunge</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Vägkant</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Vägkant mellan planterad hög  granskog och vägkant</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Thorleif Joelson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Thorleif Joelson, Henry Åkerström</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
         <is>
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>

--- a/artfynd/A 33708-2025 artfynd.xlsx
+++ b/artfynd/A 33708-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128248892</v>
       </c>
       <c r="B2" t="n">
-        <v>92402</v>
+        <v>92429</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Thorleif Joelson, Henry Åkerström</t>
+          <t>Henry Åkerström, Thorleif Joelson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -797,7 +797,7 @@
         <v>128248980</v>
       </c>
       <c r="B3" t="n">
-        <v>92402</v>
+        <v>92429</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 33708-2025 artfynd.xlsx
+++ b/artfynd/A 33708-2025 artfynd.xlsx
@@ -783,7 +783,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Henry Åkerström, Thorleif Joelson</t>
+          <t>Thorleif Joelson, Henry Åkerström</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -916,7 +916,7 @@
         <v>128832151</v>
       </c>
       <c r="B4" t="n">
-        <v>102863</v>
+        <v>102869</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 33708-2025 artfynd.xlsx
+++ b/artfynd/A 33708-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128248892</v>
       </c>
       <c r="B2" t="n">
-        <v>92429</v>
+        <v>92439</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         <v>128248980</v>
       </c>
       <c r="B3" t="n">
-        <v>92429</v>
+        <v>92439</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         <v>128832151</v>
       </c>
       <c r="B4" t="n">
-        <v>102869</v>
+        <v>102876</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 33708-2025 artfynd.xlsx
+++ b/artfynd/A 33708-2025 artfynd.xlsx
@@ -916,7 +916,7 @@
         <v>128832151</v>
       </c>
       <c r="B4" t="n">
-        <v>102876</v>
+        <v>102880</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 33708-2025 artfynd.xlsx
+++ b/artfynd/A 33708-2025 artfynd.xlsx
@@ -916,7 +916,7 @@
         <v>128832151</v>
       </c>
       <c r="B4" t="n">
-        <v>102880</v>
+        <v>102887</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 33708-2025 artfynd.xlsx
+++ b/artfynd/A 33708-2025 artfynd.xlsx
@@ -916,7 +916,7 @@
         <v>128832151</v>
       </c>
       <c r="B4" t="n">
-        <v>102895</v>
+        <v>102900</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 33708-2025 artfynd.xlsx
+++ b/artfynd/A 33708-2025 artfynd.xlsx
@@ -916,7 +916,7 @@
         <v>128832151</v>
       </c>
       <c r="B4" t="n">
-        <v>102900</v>
+        <v>102903</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 33708-2025 artfynd.xlsx
+++ b/artfynd/A 33708-2025 artfynd.xlsx
@@ -916,7 +916,7 @@
         <v>128832151</v>
       </c>
       <c r="B4" t="n">
-        <v>102903</v>
+        <v>102913</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 33708-2025 artfynd.xlsx
+++ b/artfynd/A 33708-2025 artfynd.xlsx
@@ -916,7 +916,7 @@
         <v>128832151</v>
       </c>
       <c r="B4" t="n">
-        <v>102913</v>
+        <v>102920</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 33708-2025 artfynd.xlsx
+++ b/artfynd/A 33708-2025 artfynd.xlsx
@@ -916,7 +916,7 @@
         <v>128832151</v>
       </c>
       <c r="B4" t="n">
-        <v>102920</v>
+        <v>102922</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 33708-2025 artfynd.xlsx
+++ b/artfynd/A 33708-2025 artfynd.xlsx
@@ -916,7 +916,7 @@
         <v>128832151</v>
       </c>
       <c r="B4" t="n">
-        <v>102922</v>
+        <v>102948</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 33708-2025 artfynd.xlsx
+++ b/artfynd/A 33708-2025 artfynd.xlsx
@@ -916,7 +916,7 @@
         <v>128832151</v>
       </c>
       <c r="B4" t="n">
-        <v>102948</v>
+        <v>102950</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 33708-2025 artfynd.xlsx
+++ b/artfynd/A 33708-2025 artfynd.xlsx
@@ -916,7 +916,7 @@
         <v>128832151</v>
       </c>
       <c r="B4" t="n">
-        <v>102950</v>
+        <v>102951</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
